--- a/data/trans_camb/P2A_psíq_R-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P2A_psíq_R-Habitat-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,62; 3,55</t>
+          <t>0,55; 3,55</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 1,26</t>
+          <t>-0,59; 1,42</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 1,47</t>
+          <t>-0,59; 1,43</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,5; 4,46</t>
+          <t>1,36; 4,18</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-0,1; 1,78</t>
+          <t>-0,14; 1,78</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,0; 3,11</t>
+          <t>1,0; 3,08</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,29; 3,38</t>
+          <t>1,34; 3,41</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,11; 1,3</t>
+          <t>-0,16; 1,28</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,59; 2,12</t>
+          <t>0,59; 2,06</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>15,86; 1145,04</t>
+          <t>25,99; 1289,17</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-74,67; 447,78</t>
+          <t>-60,98; 691,88</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-55,65; 548,33</t>
+          <t>-56,84; 536,54</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>136,49; 2709,47</t>
+          <t>97,85; 2507,36</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-50,88; —</t>
+          <t>-53,21; 1149,6</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>65,69; 1901,24</t>
+          <t>71,25; 2103,69</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>138,45; 1021,64</t>
+          <t>138,06; 1273,61</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-27,79; 387,34</t>
+          <t>-28,14; 425,0</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>53,44; 730,61</t>
+          <t>48,33; 720,58</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 1,48</t>
+          <t>-0,78; 1,43</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,0; 1,04</t>
+          <t>-1,05; 1,03</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,04; 1,21</t>
+          <t>-1,08; 1,26</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 1,81</t>
+          <t>-0,5; 1,65</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,72; 1,53</t>
+          <t>-0,66; 1,57</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,43; 2,61</t>
+          <t>0,52; 2,64</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,35; 1,17</t>
+          <t>-0,37; 1,2</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-0,56; 0,94</t>
+          <t>-0,49; 1,02</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-0,11; 1,64</t>
+          <t>-0,1; 1,61</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-45,11; 207,07</t>
+          <t>-47,95; 186,43</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-57,92; 152,89</t>
+          <t>-60,69; 141,2</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-54,88; 148,28</t>
+          <t>-56,72; 140,95</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-32,56; 271,44</t>
+          <t>-36,58; 240,16</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-45,51; 252,91</t>
+          <t>-41,5; 231,85</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>12,26; 377,34</t>
+          <t>23,05; 399,3</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-21,66; 128,8</t>
+          <t>-22,76; 142,25</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-35,04; 113,01</t>
+          <t>-32,82; 124,88</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-6,21; 187,26</t>
+          <t>-6,38; 187,83</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,63; 1,53</t>
+          <t>-0,5; 1,77</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 0,86</t>
+          <t>-0,94; 0,82</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,11; 4,25</t>
+          <t>1,13; 4,12</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,08; 0,46</t>
+          <t>-1,98; 0,5</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,06; 0,55</t>
+          <t>-2,06; 0,49</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,52; 54,57</t>
+          <t>0,52; 59,93</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 0,76</t>
+          <t>-0,99; 0,66</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,12; 0,41</t>
+          <t>-1,16; 0,43</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,43; 41,52</t>
+          <t>1,47; 40,77</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-80,52; 736,95</t>
+          <t>-73,68; 1222,27</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 742,76</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>52,08; 2055,87</t>
+          <t>65,14; 2618,59</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-77,22; 48,31</t>
+          <t>-75,02; 62,53</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-79,17; 61,38</t>
+          <t>-79,94; 47,45</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>26,65; 4366,96</t>
+          <t>22,4; 5536,73</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-54,66; 106,15</t>
+          <t>-59,3; 86,12</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-69,0; 63,81</t>
+          <t>-70,62; 59,75</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>97,87; 6163,85</t>
+          <t>106,58; 5993,05</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,17; 2,58</t>
+          <t>0,05; 2,63</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,1; 0,71</t>
+          <t>-1,09; 0,66</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,66; 3,52</t>
+          <t>0,74; 3,48</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,08; 2,64</t>
+          <t>0,13; 2,48</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,0; 2,32</t>
+          <t>0,01; 2,32</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,7; 3,13</t>
+          <t>0,64; 3,14</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,45; 2,18</t>
+          <t>0,41; 2,13</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,24; 1,24</t>
+          <t>-0,25; 1,24</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,04; 2,95</t>
+          <t>0,95; 2,78</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2,48; 505,52</t>
+          <t>-6,54; 482,46</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-73,53; 159,94</t>
+          <t>-75,52; 153,97</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>24,08; 617,61</t>
+          <t>35,56; 564,23</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-4,85; 332,96</t>
+          <t>4,05; 356,04</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-5,16; 316,8</t>
+          <t>-1,78; 350,54</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>34,34; 429,73</t>
+          <t>33,19; 455,81</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>27,05; 295,56</t>
+          <t>25,6; 294,88</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-19,46; 151,14</t>
+          <t>-19,4; 162,75</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>69,66; 384,66</t>
+          <t>64,01; 366,48</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,31; 1,55</t>
+          <t>0,39; 1,6</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 0,51</t>
+          <t>-0,46; 0,53</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,53; 1,9</t>
+          <t>0,48; 1,85</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,33; 1,56</t>
+          <t>0,3; 1,5</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,11; 1,02</t>
+          <t>-0,1; 1,02</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,48; 24,28</t>
+          <t>1,47; 24,08</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,48; 1,33</t>
+          <t>0,5; 1,36</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-0,13; 0,65</t>
+          <t>-0,11; 0,63</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1,26; 14,1</t>
+          <t>1,33; 13,61</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>19,85; 223,93</t>
+          <t>29,43; 224,43</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-39,25; 71,14</t>
+          <t>-40,69; 76,23</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>43,71; 266,99</t>
+          <t>39,36; 266,17</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>20,86; 164,38</t>
+          <t>19,11; 165,38</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-6,87; 112,24</t>
+          <t>-7,8; 105,94</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>120,21; 2712,32</t>
+          <t>117,93; 2563,93</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>40,07; 154,51</t>
+          <t>40,01; 162,16</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-10,64; 76,2</t>
+          <t>-10,05; 74,45</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>117,6; 1453,47</t>
+          <t>121,35; 1392,17</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P2A_psíq_R-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P2A_psíq_R-Habitat-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0,43</t>
+          <t>0,36</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,98</t>
+          <t>2,15</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>1,25</t>
+          <t>1,28</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,55; 3,55</t>
+          <t>0,57; 3,57</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,59; 1,42</t>
+          <t>-0,64; 1,36</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,59; 1,43</t>
+          <t>-0,64; 1,3</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,36; 4,18</t>
+          <t>1,34; 4,13</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-0,14; 1,78</t>
+          <t>-0,05; 1,82</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,0; 3,08</t>
+          <t>1,09; 3,31</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,34; 3,41</t>
+          <t>1,26; 3,52</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,16; 1,28</t>
+          <t>-0,1; 1,27</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,59; 2,06</t>
+          <t>0,55; 1,99</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>61,19%</t>
+          <t>50,63%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>460,2%</t>
+          <t>501,82%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>218,78%</t>
+          <t>224,63%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>25,99; 1289,17</t>
+          <t>23,25; 1171,03</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-60,98; 691,88</t>
+          <t>-67,4; 462,81</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-56,84; 536,54</t>
+          <t>-58,26; 446,62</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>97,85; 2507,36</t>
+          <t>135,79; 2743,26</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-53,21; 1149,6</t>
+          <t>-26,03; 1518,76</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>71,25; 2103,69</t>
+          <t>65,4; 1989,29</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>138,06; 1273,61</t>
+          <t>128,89; 1193,27</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-28,14; 425,0</t>
+          <t>-21,4; 410,5</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>48,33; 720,58</t>
+          <t>58,69; 683,68</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0,19</t>
+          <t>0,66</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,57</t>
+          <t>1,6</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>0,81</t>
+          <t>1,14</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,78; 1,43</t>
+          <t>-0,81; 1,32</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,05; 1,03</t>
+          <t>-1,2; 1,04</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,08; 1,26</t>
+          <t>-0,45; 1,84</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 1,65</t>
+          <t>-0,44; 1,7</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 1,57</t>
+          <t>-0,7; 1,5</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,52; 2,64</t>
+          <t>0,42; 2,71</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 1,2</t>
+          <t>-0,27; 1,26</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 1,02</t>
+          <t>-0,56; 0,98</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-0,1; 1,61</t>
+          <t>0,32; 1,92</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>53,44%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>133,24%</t>
+          <t>136,07%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>66,99%</t>
+          <t>94,03%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-47,95; 186,43</t>
+          <t>-47,47; 167,3</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-60,69; 141,2</t>
+          <t>-65,16; 152,89</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-56,72; 140,95</t>
+          <t>-29,52; 239,08</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-36,58; 240,16</t>
+          <t>-28,27; 239,69</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-41,5; 231,85</t>
+          <t>-42,54; 232,43</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>23,05; 399,3</t>
+          <t>16,46; 378,6</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-22,76; 142,25</t>
+          <t>-19,18; 156,96</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-32,82; 124,88</t>
+          <t>-35,22; 118,46</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-6,38; 187,83</t>
+          <t>17,14; 223,42</t>
         </is>
       </c>
     </row>
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>22,44</t>
+          <t>1,65</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>13,96</t>
+          <t>2,08</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 1,77</t>
+          <t>-0,41; 1,69</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,94; 0,82</t>
+          <t>-0,97; 0,82</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,13; 4,12</t>
+          <t>1,22; 4,18</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,98; 0,5</t>
+          <t>-2,11; 0,42</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,06; 0,49</t>
+          <t>-2,11; 0,48</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,52; 59,93</t>
+          <t>0,07; 3,59</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,99; 0,66</t>
+          <t>-0,89; 0,7</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,16; 0,43</t>
+          <t>-1,21; 0,39</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,47; 40,77</t>
+          <t>0,99; 3,24</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>452,24%</t>
+          <t>453,63%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1190,95%</t>
+          <t>87,41%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>1141,54%</t>
+          <t>170,4%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-73,68; 1222,27</t>
+          <t>-73,13; 828,01</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 742,76</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>65,14; 2618,59</t>
+          <t>67,33; 2050,14</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-75,02; 62,53</t>
+          <t>-76,66; 46,86</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-79,94; 47,45</t>
+          <t>-75,9; 55,64</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>22,4; 5536,73</t>
+          <t>-2,42; 309,26</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-59,3; 86,12</t>
+          <t>-55,16; 90,98</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-70,62; 59,75</t>
+          <t>-70,94; 50,62</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>106,58; 5993,05</t>
+          <t>39,45; 361,87</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1,94</t>
+          <t>1,96</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,88</t>
+          <t>2,11</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>1,91</t>
+          <t>2,04</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,05; 2,63</t>
+          <t>0,21; 2,58</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,09; 0,66</t>
+          <t>-0,96; 0,67</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,74; 3,48</t>
+          <t>0,74; 3,51</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,13; 2,48</t>
+          <t>-0,01; 2,43</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,01; 2,32</t>
+          <t>0,05; 2,4</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,64; 3,14</t>
+          <t>1,01; 3,23</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,41; 2,13</t>
+          <t>0,46; 2,18</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,25; 1,24</t>
+          <t>-0,21; 1,3</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,95; 2,78</t>
+          <t>1,3; 2,98</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>200,78%</t>
+          <t>203,15%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>158,98%</t>
+          <t>178,62%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>177,04%</t>
+          <t>189,29%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-6,54; 482,46</t>
+          <t>1,76; 503,4</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-75,52; 153,97</t>
+          <t>-72,03; 124,54</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>35,56; 564,23</t>
+          <t>29,32; 611,3</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4,05; 356,04</t>
+          <t>-7,2; 311,73</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-1,78; 350,54</t>
+          <t>-4,05; 299,77</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>33,19; 455,81</t>
+          <t>47,08; 448,56</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>25,6; 294,88</t>
+          <t>26,4; 288,5</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-19,4; 162,75</t>
+          <t>-17,63; 171,35</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>64,01; 366,48</t>
+          <t>79,85; 405,03</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>1,39</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>7,03</t>
+          <t>1,89</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>4,22</t>
+          <t>1,65</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,39; 1,6</t>
+          <t>0,32; 1,52</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 0,53</t>
+          <t>-0,48; 0,49</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,48; 1,85</t>
+          <t>0,81; 2,06</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,3; 1,5</t>
+          <t>0,33; 1,53</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,1; 1,02</t>
+          <t>-0,14; 1,04</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,47; 24,08</t>
+          <t>1,26; 2,57</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,5; 1,36</t>
+          <t>0,55; 1,39</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-0,11; 0,63</t>
+          <t>-0,15; 0,61</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1,33; 13,61</t>
+          <t>1,22; 2,12</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>132,4%</t>
+          <t>152,9%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>601,53%</t>
+          <t>161,51%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>405,74%</t>
+          <t>158,27%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>29,43; 224,43</t>
+          <t>26,49; 220,44</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-40,69; 76,23</t>
+          <t>-41,21; 70,95</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>39,36; 266,17</t>
+          <t>69,69; 299,64</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>19,11; 165,38</t>
+          <t>22,25; 170,84</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-7,8; 105,94</t>
+          <t>-10,84; 111,47</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>117,93; 2563,93</t>
+          <t>86,65; 294,24</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>40,01; 162,16</t>
+          <t>43,39; 159,19</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-10,05; 74,45</t>
+          <t>-12,99; 69,48</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>121,35; 1392,17</t>
+          <t>96,3; 245,16</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P2A_psíq_R-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P2A_psíq_R-Habitat-trans_camb.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas con limitación por discapacidad psíquica</t>
+          <t>Población que convive con personas con alguna limitación por discapacidad psíquica</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
